--- a/artfynd/S 4458-2023 artfynd.xlsx
+++ b/artfynd/S 4458-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ2"/>
+  <dimension ref="A1:AZ3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -680,10 +680,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>63457111</v>
+        <v>137073694</v>
       </c>
       <c r="B2" t="n">
-        <v>104807</v>
+        <v>90012</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,37 +691,40 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220464</v>
+        <v>2979</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lundbräsma</t>
+          <t>Lömsk flugsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Cardamine impatiens</t>
+          <t>Amanita phalloides</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.:Fr.) Link</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>600m SO Slättön, Sk</t>
+          <t>Barnakälla vid parkeringen, Sk</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>469388</v>
+        <v>469927</v>
       </c>
       <c r="R2" t="n">
-        <v>6220293</v>
+        <v>6220636</v>
       </c>
       <c r="S2" t="n">
-        <v>100</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,17 +748,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2000-08-27</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2000-08-27</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Cardamine impatiens/3E4d2843/Ivetofta s:n/ANi/ /Allan Nicklasson,Växjö</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -764,36 +762,144 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>vägslänt</t>
-        </is>
-      </c>
-      <c r="AR2" t="inlineStr">
-        <is>
-          <t>SkFlora    618663</t>
-        </is>
-      </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
+          <t>Gunilla Svensson</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>Gunilla Svensson</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137073694</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>63457111</v>
+      </c>
+      <c r="B3" t="n">
+        <v>104807</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>220464</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Lundbräsma</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Cardamine impatiens</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>600m SO Slättön, Sk</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>469388</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6220293</v>
+      </c>
+      <c r="S3" t="n">
+        <v>100</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Bromölla</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Ivetofta</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2000-08-27</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2000-08-27</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Cardamine impatiens/3E4d2843/Ivetofta s:n/ANi/ /Allan Nicklasson,Växjö</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>vägslänt</t>
+        </is>
+      </c>
+      <c r="AR3" t="inlineStr">
+        <is>
+          <t>SkFlora    618663</t>
+        </is>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
           <t>Charlotte Wigermo</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr">
+      <c r="AX3" t="inlineStr">
         <is>
           <t>Allan Nicklasson</t>
         </is>
       </c>
-      <c r="AY2" t="inlineStr">
+      <c r="AY3" t="inlineStr">
         <is>
           <t>Skånes Flora (1989-2006)</t>
         </is>
       </c>
-      <c r="AZ2" t="inlineStr">
+      <c r="AZ3" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/63457111</t>
         </is>
@@ -802,6 +908,7 @@
   </sheetData>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/S 4458-2023 artfynd.xlsx
+++ b/artfynd/S 4458-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137073694</v>
       </c>
       <c r="B2" t="n">
-        <v>90012</v>
+        <v>90013</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/S 4458-2023 artfynd.xlsx
+++ b/artfynd/S 4458-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137073694</v>
       </c>
       <c r="B2" t="n">
-        <v>90013</v>
+        <v>90019</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/S 4458-2023 artfynd.xlsx
+++ b/artfynd/S 4458-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137073694</v>
       </c>
       <c r="B2" t="n">
-        <v>90019</v>
+        <v>90023</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/S 4458-2023 artfynd.xlsx
+++ b/artfynd/S 4458-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137073694</v>
       </c>
       <c r="B2" t="n">
-        <v>90023</v>
+        <v>90025</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/S 4458-2023 artfynd.xlsx
+++ b/artfynd/S 4458-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137073694</v>
       </c>
       <c r="B2" t="n">
-        <v>90025</v>
+        <v>90038</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/S 4458-2023 artfynd.xlsx
+++ b/artfynd/S 4458-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137073694</v>
       </c>
       <c r="B2" t="n">
-        <v>90038</v>
+        <v>90040</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/S 4458-2023 artfynd.xlsx
+++ b/artfynd/S 4458-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137073694</v>
       </c>
       <c r="B2" t="n">
-        <v>90040</v>
+        <v>90043</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/S 4458-2023 artfynd.xlsx
+++ b/artfynd/S 4458-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137073694</v>
       </c>
       <c r="B2" t="n">
-        <v>90043</v>
+        <v>90053</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/S 4458-2023 artfynd.xlsx
+++ b/artfynd/S 4458-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137073694</v>
       </c>
       <c r="B2" t="n">
-        <v>90053</v>
+        <v>90054</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/S 4458-2023 artfynd.xlsx
+++ b/artfynd/S 4458-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137073694</v>
       </c>
       <c r="B2" t="n">
-        <v>90054</v>
+        <v>90057</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/S 4458-2023 artfynd.xlsx
+++ b/artfynd/S 4458-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137073694</v>
       </c>
       <c r="B2" t="n">
-        <v>90057</v>
+        <v>90062</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/S 4458-2023 artfynd.xlsx
+++ b/artfynd/S 4458-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137073694</v>
       </c>
       <c r="B2" t="n">
-        <v>90062</v>
+        <v>90073</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/S 4458-2023 artfynd.xlsx
+++ b/artfynd/S 4458-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137073694</v>
       </c>
       <c r="B2" t="n">
-        <v>90073</v>
+        <v>90074</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/S 4458-2023 artfynd.xlsx
+++ b/artfynd/S 4458-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137073694</v>
       </c>
       <c r="B2" t="n">
-        <v>90074</v>
+        <v>90077</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/S 4458-2023 artfynd.xlsx
+++ b/artfynd/S 4458-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137073694</v>
       </c>
       <c r="B2" t="n">
-        <v>90077</v>
+        <v>90081</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
